--- a/data/trading_post.xlsx
+++ b/data/trading_post.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -499,16 +499,14 @@
           <t>Big Hat</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>https://begoldenfarms.com/store/big-hat</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Added 2026-09-18 per Laurie. Image auto-fetched from the product page (OG image) unless a URL is put in the Image column.</t>
+          <t>Added 2026-09-18 per Laurie. Image auto-fetched from the product page (OG image) unless a URL is put in the Image column. | 2026-09-18: begoldenfarms.com blocks automated fetching (robots), so NO image or price can be pulled — Laurie to paste an image URL and price by hand.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -538,16 +536,14 @@
           <t>Jellybeanie — 100% Be Golden Farms wool beanie</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>https://begoldenfarms.com/store/jellybeanie-100-be-golden-farms-wool-beanie</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Added 2026-09-18 per Laurie.</t>
+          <t>Added 2026-09-18 per Laurie. | 2026-09-18: begoldenfarms.com blocks automated fetching (robots), so NO image or price can be pulled — Laurie to paste an image URL and price by hand.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -574,22 +570,539 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mountain Spring Yoda Soap</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>Catskill Body Bar</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>$11</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>https://www.apothecasy.com/products/mountain-spring-yoda-soap?variant=44813506871605</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.apothecasy.com/cdn/shop/files/image_43e798ab-4998-4edc-82f8-02c1d81f431a.jpg?v=1695090407&amp;width=1024</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Added 2026-09-18 per Laurie (not clothing — filed under Bath &amp; Body).</t>
+          <t>Added 2026-09-18 per Laurie (not clothing — filed under Bath &amp; Body). | 2026-09-18: renamed to Catskill Body Bar (the shop renamed it; URL unchanged). Price $11 from the page. Image set manually: the page's OG image is a .heic, which browsers other than Safari cannot show.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Provisions</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Heather Ridge Farm</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Preston Hollow</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Patent Root Beer Syrup</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>$46 (4 × 16 oz)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://heather-ridge-farm.com/product/patent-root-beer-syrup/</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://heather-ridge-farm.com/wp-content/uploads/2017/05/root-beer-syrup.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Added 2026-09-18 per Laurie — first Provisions item. Town from the POI master (Heather Ridge Farm, Preston Hollow). | 2026-09-18: price $46 for a 4-bottle case, image from the page.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bath &amp; Body</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Windswept Farm Botanicals</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Cobleskill</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Folk Salve — Calendula (2 oz)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>$18</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/listing/1645657704/folk-salve-calendula</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://i.etsystatic.com/6633974/r/il/58676f/5926239828/il_1080xN.5926239828_d34l.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Added 2026-09-18 per Laurie. Etsy shop WindsweptBotanicals (Jessica Capeci; 14 yrs on Etsy, 4.9). Price + image from the listing (Etsy exposes product:price:amount, so future Etsy rows can leave Price blank). Label reads Seward, NY; ships from Cobleskill.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Provisions</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rockerbox Spice Co.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Berne</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Rockerbox Spices</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://rockerboxspiceco.com/products/rockerbox-spices</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Added 2026-09-18 per Laurie. Town from the POI master. Image + price auto-fetched at build (Shopify).</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Better Days Bookshop</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Cat's Cradle — Kurt Vonnegut</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://betterdaysbookshop.com/item/rZT5HAYCeafyyAcBnHhHTQ</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://bookmanager.com/i/m?b=rZT5HAYCeafyyAcBnHhHTQ</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Added 2026-09-18 per Laurie. Title + cover from the page (Bookmanager storefront; no price tag exposed — Laurie may add).</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bookshop.org</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>First Person Singular — Haruki Murakami</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://bookshop.org/p/books/the-first-person-singular-haruki-murakami/f6fc9c5bdba711bd?ean=9780593311189</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Added 2026-09-18 per Laurie. Bookshop.org routes purchases to independent bookstores; no town. Image/price auto-fetched at build.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Gift Cards &amp; Experiences</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bard &amp; Baker Board Game Cafe</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Troy</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Gift cards &amp; online store</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.bardandbaker.com/online-store</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Added 2026-09-18 per Laurie. Store landing page rather than a single product; image auto-fetched (site OG image).</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Big Emotions Studio</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Albany</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fisher Daddy Sweater — hand-knit, unisex M–2X</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>$250</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://bigemotionsstudio.com/shop/p/cixxrc1pi34gf7scc1mqc07qxrh6d5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://static1.squarespace.com/static/623b74fc41cfe25664fd5d8c/623f6f2c2625ae5261f195ea/65d634ca235b060c971dff3f/1708537049115/F2E91DA2-15DC-4761-81F1-B74B991DC4DD?format=1500w</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Added 2026-09-18 per Laurie. Price + image from the page (Squarespace). Listing shows SOLD OUT at time of add — one-of-a-kind pieces; the shop button still works for the studio. Town from the POI master (Big Emotions Vintage Shop and Sewing Studio, 296 Delaware Ave, Albany).</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Provisions</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Biscuitwood Farm</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Esperance</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Farmer Meg's Potato &amp; Cheese Pierogi — 24 frozen, with onion confit &amp; sour cream (bulk pre-order; pickup on/after Sept 25)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://biscuitwoodfarm.square.site/product/farmer-meg-s-potato-and-cheese-pierogi-bulk-pre-order-pick-up-on-or-after-september-25th-/263?cs=true&amp;cst=custom</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://130404605.cdn6.editmysite.com/uploads/1/3/0/4/130404605/FF3GTIPJTZSNTIN67P2W36VV.jpeg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Added 2026-09-18 per Laurie. Image from the page (Square Online; no price meta exposed — Laurie to add). Farm-grown potatoes, made in a certified kitchen; limit 2 orders. Pre-order/pickup item — consider Display=No after the pickup window passes.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Camp Catskill</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Tannersville</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Kahtoola MICROspikes — ice traction, red (XS–XL)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>$83.95</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://campcatskill.co/collections/snowsports/products/microspikes</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://campcatskill.co/cdn/shop/files/18_source_1674168171.jpg?v=1763516193</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Added 2026-09-18 per Laurie. Price + image from the page (Shopify). Independent outfitter, 6006 Main St Tannersville; 1% for the Planet member. Note: the spikes themselves are Kahtoola (Flagstaff AZ), not locally made — the local part is the shop. M and L sold out at time of add.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Bath &amp; Body</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Carr's Creek Soaps</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Berne</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Bar Soap, 4 oz</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://carrscreeksoaps.square.site/product/bar-soap-4-oz/</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Added 2026-09-18 per Laurie. Square Online storefront exposes no product image or price meta (page is JS-rendered) — Laurie to paste an image URL and price; card shows the 🛍️ placeholder until then. Town from the POI master (761 Gifford Hollow Rd, Berne).</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Bath &amp; Body</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mustard &amp; Miel</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Catskill</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lip Balm — organic beeswax, honey &amp; olive oil, ½ oz</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>$6</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://mustardandmiel.com/products/lip-balm</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://mustardandmiel.com/cdn/shop/files/LipBalmA.jpg?v=1764797259</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Added 2026-09-18 per Laurie. Price + image from the page (Shopify). Recipe from their Hudson Valley beekeeping family. Town from the POI master (Catskill).</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Provisions</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Atina Foods</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Catskill</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Locavore New York 3-Pack — Rhubarb Ginger Herbal Jam, Fennel, Green Tomato Pickle</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>$44</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://www.atinafoods.com/museum/locavoreny</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://static1.squarespace.com/static/5888051cd2b857f7b002e24f/58f13adbb3db2bed6e911aed/68ffa7efa441d622af773555/1780400329517/Screenshot+2025-10-27+at+13.25.59.png?format=1500w</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Added 2026-09-18 per Laurie. Price + image from the page (Squarespace). Jars sold by the 3-pack only.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
